--- a/DesignData/Excel_Masters/StageStats_Master.xlsx
+++ b/DesignData/Excel_Masters/StageStats_Master.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealCpp\Paradise\DesignData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Documents\Unreal Projects\ProjectParadise\DesignData\Excel_Masters\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,15 +14,12 @@
   <sheets>
     <sheet name="StageStats_Master" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t>---</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="69">
   <si>
     <t>NextStageID</t>
   </si>
@@ -40,6 +37,196 @@
   </si>
   <si>
     <t>Description</t>
+  </si>
+  <si>
+    <t>Stage1_1</t>
+  </si>
+  <si>
+    <t>Stage1_2</t>
+  </si>
+  <si>
+    <t>Stage1_3</t>
+  </si>
+  <si>
+    <t>Stage1_4</t>
+  </si>
+  <si>
+    <t>Stage1_5</t>
+  </si>
+  <si>
+    <t>Stage1_6</t>
+  </si>
+  <si>
+    <t>Stage1_7</t>
+  </si>
+  <si>
+    <t>Stage1_8</t>
+  </si>
+  <si>
+    <t>Stage1_9</t>
+  </si>
+  <si>
+    <t>Stage1_10</t>
+  </si>
+  <si>
+    <t>Stage2_1</t>
+  </si>
+  <si>
+    <t>Stage2_2</t>
+  </si>
+  <si>
+    <t>Stage2_3</t>
+  </si>
+  <si>
+    <t>Stage2_4</t>
+  </si>
+  <si>
+    <t>Stage2_5</t>
+  </si>
+  <si>
+    <t>Stage2_6</t>
+  </si>
+  <si>
+    <t>Stage2_7</t>
+  </si>
+  <si>
+    <t>Stage2_8</t>
+  </si>
+  <si>
+    <t>Stage2_9</t>
+  </si>
+  <si>
+    <t>Stage2_10</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>숲의 입구</t>
+  </si>
+  <si>
+    <t>모험이 시작되는 평화로운 숲의 입구입니다. 가벼운 몬스터들이 등장합니다.</t>
+  </si>
+  <si>
+    <t>고요한 오솔길</t>
+  </si>
+  <si>
+    <t>인적이 드문 오솔길입니다. 몬스터들의 움직임이 조금씩 활발해집니다.</t>
+  </si>
+  <si>
+    <t>이끼 낀 바위지대</t>
+  </si>
+  <si>
+    <t>미끄러운 이끼가 낀 바위들이 널려있습니다. 기습에 주의하세요.</t>
+  </si>
+  <si>
+    <t>안개 낀 덩굴 숲</t>
+  </si>
+  <si>
+    <t>시야를 가리는 짙은 안개와 가시 덩굴이 길을 막고 있습니다.</t>
+  </si>
+  <si>
+    <t>숲의 파수꾼 (중간 보스)</t>
+  </si>
+  <si>
+    <t>숲을 지키는 거대한 파수꾼이 길을 가로막습니다. 튼튼한 방어력이 특징입니다.</t>
+  </si>
+  <si>
+    <t>어두워진 숲길</t>
+  </si>
+  <si>
+    <t>나무들이 우거져 햇빛이 들지 않는 어두운 길입니다.</t>
+  </si>
+  <si>
+    <t>환영의 빈터</t>
+  </si>
+  <si>
+    <t>방향 감각을 상실하게 만드는 기묘한 기운이 흐르는 빈터입니다.</t>
+  </si>
+  <si>
+    <t>오염된 샘물</t>
+  </si>
+  <si>
+    <t>맑았던 샘물이 몬스터들에 의해 오염되었습니다. 적들을 처치하여 정화하세요.</t>
+  </si>
+  <si>
+    <t>수호자의 둥지 입구</t>
+  </si>
+  <si>
+    <t>거대한 마력이 느껴지는 둥지 입구입니다. 보스와의 결전이 머지않았습니다.</t>
+  </si>
+  <si>
+    <t>숲의 지배자 (보스)</t>
+  </si>
+  <si>
+    <t>속삭이는 숲의 거대한 지배자가 깨어났습니다. 모든 힘을 다해 처치하세요!</t>
+  </si>
+  <si>
+    <t>잊혀진 유적 입구</t>
+  </si>
+  <si>
+    <t>고대 문명의 흔적이 남아있는 거대한 유적의 입구입니다.</t>
+  </si>
+  <si>
+    <t>먼지 덮인 회랑</t>
+  </si>
+  <si>
+    <t>오랜 세월 동안 방치된 회랑입니다. 기계 타입 몬스터가 등장하기 시작합니다.</t>
+  </si>
+  <si>
+    <t>함정의 방</t>
+  </si>
+  <si>
+    <t>침입자를 막기 위해 설계된 고대의 방어 장치들이 작동합니다.</t>
+  </si>
+  <si>
+    <t>고대 병사의 무덤</t>
+  </si>
+  <si>
+    <t>유적을 지키다 잠든 병사들의 원령이 떠돌고 있습니다.</t>
+  </si>
+  <si>
+    <t>유적 수문장 (중간 보스)</t>
+  </si>
+  <si>
+    <t>강철로 이루어진 거대한 수문장이 유적 깊은 곳으로 향하는 길을 막습니다.</t>
+  </si>
+  <si>
+    <t>끝없는 계단</t>
+  </si>
+  <si>
+    <t>지하로 깊게 이어지는 나선형 계단입니다. 적들의 저항이 거세집니다.</t>
+  </si>
+  <si>
+    <t>마력 동력실</t>
+  </si>
+  <si>
+    <t>유적의 에너지를 공급하는 곳입니다. 폭발하는 적들을 조심하세요.</t>
+  </si>
+  <si>
+    <t>어둠이 스민 복도</t>
+  </si>
+  <si>
+    <t>유적의 심층부에서 흘러나오는 어둠의 기운이 가득한 복도입니다.</t>
+  </si>
+  <si>
+    <t>군주의 알현실 입구</t>
+  </si>
+  <si>
+    <t>유적의 주인이 잠들어 있는 알현실로 통하는 거대한 문 앞입니다.</t>
+  </si>
+  <si>
+    <t>고대의 군주 (보스)</t>
+  </si>
+  <si>
+    <t>오랜 잠에서 깨어난 고대의 군주가 분노합니다. 진정한 시험의 무대입니다!</t>
+  </si>
+  <si>
+    <t>ClearAether</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -957,34 +1144,558 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>90</v>
+      </c>
+      <c r="D2">
+        <v>100</v>
+      </c>
+      <c r="E2">
+        <v>1000</v>
+      </c>
+      <c r="F2">
+        <v>50</v>
+      </c>
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3">
+        <v>90</v>
+      </c>
+      <c r="D3">
+        <v>120</v>
+      </c>
+      <c r="E3">
+        <v>1000</v>
+      </c>
+      <c r="F3">
+        <v>60</v>
+      </c>
+      <c r="G3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4">
+        <v>90</v>
+      </c>
+      <c r="D4">
+        <v>140</v>
+      </c>
+      <c r="E4">
+        <v>1000</v>
+      </c>
+      <c r="F4">
+        <v>70</v>
+      </c>
+      <c r="G4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>90</v>
+      </c>
+      <c r="D5">
+        <v>160</v>
+      </c>
+      <c r="E5">
+        <v>1000</v>
+      </c>
+      <c r="F5">
+        <v>80</v>
+      </c>
+      <c r="G5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>120</v>
+      </c>
+      <c r="D6">
+        <v>300</v>
+      </c>
+      <c r="E6">
+        <v>1000</v>
+      </c>
+      <c r="F6">
+        <v>150</v>
+      </c>
+      <c r="G6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>90</v>
+      </c>
+      <c r="D7">
+        <v>180</v>
+      </c>
+      <c r="E7">
+        <v>1000</v>
+      </c>
+      <c r="F7">
+        <v>90</v>
+      </c>
+      <c r="G7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>90</v>
+      </c>
+      <c r="D8">
+        <v>200</v>
+      </c>
+      <c r="E8">
+        <v>1000</v>
+      </c>
+      <c r="F8">
+        <v>100</v>
+      </c>
+      <c r="G8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>90</v>
+      </c>
+      <c r="D9">
+        <v>220</v>
+      </c>
+      <c r="E9">
+        <v>1000</v>
+      </c>
+      <c r="F9">
+        <v>110</v>
+      </c>
+      <c r="G9" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>90</v>
+      </c>
+      <c r="D10">
+        <v>240</v>
+      </c>
+      <c r="E10">
+        <v>1000</v>
+      </c>
+      <c r="F10">
+        <v>120</v>
+      </c>
+      <c r="G10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>180</v>
+      </c>
+      <c r="D11">
+        <v>600</v>
+      </c>
+      <c r="E11">
+        <v>1000</v>
+      </c>
+      <c r="F11">
+        <v>300</v>
+      </c>
+      <c r="G11" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12">
+        <v>90</v>
+      </c>
+      <c r="D12">
+        <v>260</v>
+      </c>
+      <c r="E12">
+        <v>1000</v>
+      </c>
+      <c r="F12">
+        <v>130</v>
+      </c>
+      <c r="G12" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13">
+        <v>90</v>
+      </c>
+      <c r="D13">
+        <v>280</v>
+      </c>
+      <c r="E13">
+        <v>1000</v>
+      </c>
+      <c r="F13">
+        <v>140</v>
+      </c>
+      <c r="G13" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14">
+        <v>90</v>
+      </c>
+      <c r="D14">
+        <v>300</v>
+      </c>
+      <c r="E14">
+        <v>1000</v>
+      </c>
+      <c r="F14">
+        <v>150</v>
+      </c>
+      <c r="G14" t="s">
+        <v>52</v>
+      </c>
+      <c r="H14" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15">
+        <v>90</v>
+      </c>
+      <c r="D15">
+        <v>320</v>
+      </c>
+      <c r="E15">
+        <v>1000</v>
+      </c>
+      <c r="F15">
+        <v>160</v>
+      </c>
+      <c r="G15" t="s">
+        <v>54</v>
+      </c>
+      <c r="H15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16">
+        <v>120</v>
+      </c>
+      <c r="D16">
+        <v>500</v>
+      </c>
+      <c r="E16">
+        <v>1000</v>
+      </c>
+      <c r="F16">
+        <v>250</v>
+      </c>
+      <c r="G16" t="s">
+        <v>56</v>
+      </c>
+      <c r="H16" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17">
+        <v>90</v>
+      </c>
+      <c r="D17">
+        <v>340</v>
+      </c>
+      <c r="E17">
+        <v>1000</v>
+      </c>
+      <c r="F17">
+        <v>170</v>
+      </c>
+      <c r="G17" t="s">
+        <v>58</v>
+      </c>
+      <c r="H17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18">
+        <v>90</v>
+      </c>
+      <c r="D18">
+        <v>360</v>
+      </c>
+      <c r="E18">
+        <v>1000</v>
+      </c>
+      <c r="F18">
+        <v>180</v>
+      </c>
+      <c r="G18" t="s">
+        <v>60</v>
+      </c>
+      <c r="H18" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19">
+        <v>90</v>
+      </c>
+      <c r="D19">
+        <v>380</v>
+      </c>
+      <c r="E19">
+        <v>1000</v>
+      </c>
+      <c r="F19">
+        <v>190</v>
+      </c>
+      <c r="G19" t="s">
+        <v>62</v>
+      </c>
+      <c r="H19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20">
+        <v>90</v>
+      </c>
+      <c r="D20">
+        <v>400</v>
+      </c>
+      <c r="E20">
+        <v>1000</v>
+      </c>
+      <c r="F20">
+        <v>200</v>
+      </c>
+      <c r="G20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H20" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21">
+        <v>180</v>
+      </c>
+      <c r="D21">
+        <v>1000</v>
+      </c>
+      <c r="E21">
+        <v>1000</v>
+      </c>
+      <c r="F21">
+        <v>500</v>
+      </c>
+      <c r="G21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H21" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/DesignData/Excel_Masters/StageStats_Master.xlsx
+++ b/DesignData/Excel_Masters/StageStats_Master.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KGA\Documents\Unreal Projects\ProjectParadise\DesignData\Excel_Masters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnrealCpp\Paradise\DesignData\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,12 +14,15 @@
   <sheets>
     <sheet name="StageStats_Master" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+  <si>
+    <t>---</t>
+  </si>
   <si>
     <t>NextStageID</t>
   </si>
@@ -37,196 +40,6 @@
   </si>
   <si>
     <t>Description</t>
-  </si>
-  <si>
-    <t>Stage1_1</t>
-  </si>
-  <si>
-    <t>Stage1_2</t>
-  </si>
-  <si>
-    <t>Stage1_3</t>
-  </si>
-  <si>
-    <t>Stage1_4</t>
-  </si>
-  <si>
-    <t>Stage1_5</t>
-  </si>
-  <si>
-    <t>Stage1_6</t>
-  </si>
-  <si>
-    <t>Stage1_7</t>
-  </si>
-  <si>
-    <t>Stage1_8</t>
-  </si>
-  <si>
-    <t>Stage1_9</t>
-  </si>
-  <si>
-    <t>Stage1_10</t>
-  </si>
-  <si>
-    <t>Stage2_1</t>
-  </si>
-  <si>
-    <t>Stage2_2</t>
-  </si>
-  <si>
-    <t>Stage2_3</t>
-  </si>
-  <si>
-    <t>Stage2_4</t>
-  </si>
-  <si>
-    <t>Stage2_5</t>
-  </si>
-  <si>
-    <t>Stage2_6</t>
-  </si>
-  <si>
-    <t>Stage2_7</t>
-  </si>
-  <si>
-    <t>Stage2_8</t>
-  </si>
-  <si>
-    <t>Stage2_9</t>
-  </si>
-  <si>
-    <t>Stage2_10</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>숲의 입구</t>
-  </si>
-  <si>
-    <t>모험이 시작되는 평화로운 숲의 입구입니다. 가벼운 몬스터들이 등장합니다.</t>
-  </si>
-  <si>
-    <t>고요한 오솔길</t>
-  </si>
-  <si>
-    <t>인적이 드문 오솔길입니다. 몬스터들의 움직임이 조금씩 활발해집니다.</t>
-  </si>
-  <si>
-    <t>이끼 낀 바위지대</t>
-  </si>
-  <si>
-    <t>미끄러운 이끼가 낀 바위들이 널려있습니다. 기습에 주의하세요.</t>
-  </si>
-  <si>
-    <t>안개 낀 덩굴 숲</t>
-  </si>
-  <si>
-    <t>시야를 가리는 짙은 안개와 가시 덩굴이 길을 막고 있습니다.</t>
-  </si>
-  <si>
-    <t>숲의 파수꾼 (중간 보스)</t>
-  </si>
-  <si>
-    <t>숲을 지키는 거대한 파수꾼이 길을 가로막습니다. 튼튼한 방어력이 특징입니다.</t>
-  </si>
-  <si>
-    <t>어두워진 숲길</t>
-  </si>
-  <si>
-    <t>나무들이 우거져 햇빛이 들지 않는 어두운 길입니다.</t>
-  </si>
-  <si>
-    <t>환영의 빈터</t>
-  </si>
-  <si>
-    <t>방향 감각을 상실하게 만드는 기묘한 기운이 흐르는 빈터입니다.</t>
-  </si>
-  <si>
-    <t>오염된 샘물</t>
-  </si>
-  <si>
-    <t>맑았던 샘물이 몬스터들에 의해 오염되었습니다. 적들을 처치하여 정화하세요.</t>
-  </si>
-  <si>
-    <t>수호자의 둥지 입구</t>
-  </si>
-  <si>
-    <t>거대한 마력이 느껴지는 둥지 입구입니다. 보스와의 결전이 머지않았습니다.</t>
-  </si>
-  <si>
-    <t>숲의 지배자 (보스)</t>
-  </si>
-  <si>
-    <t>속삭이는 숲의 거대한 지배자가 깨어났습니다. 모든 힘을 다해 처치하세요!</t>
-  </si>
-  <si>
-    <t>잊혀진 유적 입구</t>
-  </si>
-  <si>
-    <t>고대 문명의 흔적이 남아있는 거대한 유적의 입구입니다.</t>
-  </si>
-  <si>
-    <t>먼지 덮인 회랑</t>
-  </si>
-  <si>
-    <t>오랜 세월 동안 방치된 회랑입니다. 기계 타입 몬스터가 등장하기 시작합니다.</t>
-  </si>
-  <si>
-    <t>함정의 방</t>
-  </si>
-  <si>
-    <t>침입자를 막기 위해 설계된 고대의 방어 장치들이 작동합니다.</t>
-  </si>
-  <si>
-    <t>고대 병사의 무덤</t>
-  </si>
-  <si>
-    <t>유적을 지키다 잠든 병사들의 원령이 떠돌고 있습니다.</t>
-  </si>
-  <si>
-    <t>유적 수문장 (중간 보스)</t>
-  </si>
-  <si>
-    <t>강철로 이루어진 거대한 수문장이 유적 깊은 곳으로 향하는 길을 막습니다.</t>
-  </si>
-  <si>
-    <t>끝없는 계단</t>
-  </si>
-  <si>
-    <t>지하로 깊게 이어지는 나선형 계단입니다. 적들의 저항이 거세집니다.</t>
-  </si>
-  <si>
-    <t>마력 동력실</t>
-  </si>
-  <si>
-    <t>유적의 에너지를 공급하는 곳입니다. 폭발하는 적들을 조심하세요.</t>
-  </si>
-  <si>
-    <t>어둠이 스민 복도</t>
-  </si>
-  <si>
-    <t>유적의 심층부에서 흘러나오는 어둠의 기운이 가득한 복도입니다.</t>
-  </si>
-  <si>
-    <t>군주의 알현실 입구</t>
-  </si>
-  <si>
-    <t>유적의 주인이 잠들어 있는 알현실로 통하는 거대한 문 앞입니다.</t>
-  </si>
-  <si>
-    <t>고대의 군주 (보스)</t>
-  </si>
-  <si>
-    <t>오랜 잠에서 깨어난 고대의 군주가 분노합니다. 진정한 시험의 무대입니다!</t>
-  </si>
-  <si>
-    <t>ClearAether</t>
-    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1144,558 +957,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
         <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2">
-        <v>90</v>
-      </c>
-      <c r="D2">
-        <v>100</v>
-      </c>
-      <c r="E2">
-        <v>1000</v>
-      </c>
-      <c r="F2">
-        <v>50</v>
-      </c>
-      <c r="G2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3">
-        <v>90</v>
-      </c>
-      <c r="D3">
-        <v>120</v>
-      </c>
-      <c r="E3">
-        <v>1000</v>
-      </c>
-      <c r="F3">
-        <v>60</v>
-      </c>
-      <c r="G3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4">
-        <v>90</v>
-      </c>
-      <c r="D4">
-        <v>140</v>
-      </c>
-      <c r="E4">
-        <v>1000</v>
-      </c>
-      <c r="F4">
-        <v>70</v>
-      </c>
-      <c r="G4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5">
-        <v>90</v>
-      </c>
-      <c r="D5">
-        <v>160</v>
-      </c>
-      <c r="E5">
-        <v>1000</v>
-      </c>
-      <c r="F5">
-        <v>80</v>
-      </c>
-      <c r="G5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6">
-        <v>120</v>
-      </c>
-      <c r="D6">
-        <v>300</v>
-      </c>
-      <c r="E6">
-        <v>1000</v>
-      </c>
-      <c r="F6">
-        <v>150</v>
-      </c>
-      <c r="G6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7">
-        <v>90</v>
-      </c>
-      <c r="D7">
-        <v>180</v>
-      </c>
-      <c r="E7">
-        <v>1000</v>
-      </c>
-      <c r="F7">
-        <v>90</v>
-      </c>
-      <c r="G7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8">
-        <v>90</v>
-      </c>
-      <c r="D8">
-        <v>200</v>
-      </c>
-      <c r="E8">
-        <v>1000</v>
-      </c>
-      <c r="F8">
-        <v>100</v>
-      </c>
-      <c r="G8" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9">
-        <v>90</v>
-      </c>
-      <c r="D9">
-        <v>220</v>
-      </c>
-      <c r="E9">
-        <v>1000</v>
-      </c>
-      <c r="F9">
-        <v>110</v>
-      </c>
-      <c r="G9" t="s">
-        <v>42</v>
-      </c>
-      <c r="H9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10">
-        <v>90</v>
-      </c>
-      <c r="D10">
-        <v>240</v>
-      </c>
-      <c r="E10">
-        <v>1000</v>
-      </c>
-      <c r="F10">
-        <v>120</v>
-      </c>
-      <c r="G10" t="s">
-        <v>44</v>
-      </c>
-      <c r="H10" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11">
-        <v>180</v>
-      </c>
-      <c r="D11">
-        <v>600</v>
-      </c>
-      <c r="E11">
-        <v>1000</v>
-      </c>
-      <c r="F11">
-        <v>300</v>
-      </c>
-      <c r="G11" t="s">
-        <v>46</v>
-      </c>
-      <c r="H11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12">
-        <v>90</v>
-      </c>
-      <c r="D12">
-        <v>260</v>
-      </c>
-      <c r="E12">
-        <v>1000</v>
-      </c>
-      <c r="F12">
-        <v>130</v>
-      </c>
-      <c r="G12" t="s">
-        <v>48</v>
-      </c>
-      <c r="H12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13">
-        <v>90</v>
-      </c>
-      <c r="D13">
-        <v>280</v>
-      </c>
-      <c r="E13">
-        <v>1000</v>
-      </c>
-      <c r="F13">
-        <v>140</v>
-      </c>
-      <c r="G13" t="s">
-        <v>50</v>
-      </c>
-      <c r="H13" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14">
-        <v>90</v>
-      </c>
-      <c r="D14">
-        <v>300</v>
-      </c>
-      <c r="E14">
-        <v>1000</v>
-      </c>
-      <c r="F14">
-        <v>150</v>
-      </c>
-      <c r="G14" t="s">
-        <v>52</v>
-      </c>
-      <c r="H14" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15">
-        <v>90</v>
-      </c>
-      <c r="D15">
-        <v>320</v>
-      </c>
-      <c r="E15">
-        <v>1000</v>
-      </c>
-      <c r="F15">
-        <v>160</v>
-      </c>
-      <c r="G15" t="s">
-        <v>54</v>
-      </c>
-      <c r="H15" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16">
-        <v>120</v>
-      </c>
-      <c r="D16">
-        <v>500</v>
-      </c>
-      <c r="E16">
-        <v>1000</v>
-      </c>
-      <c r="F16">
-        <v>250</v>
-      </c>
-      <c r="G16" t="s">
-        <v>56</v>
-      </c>
-      <c r="H16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17">
-        <v>90</v>
-      </c>
-      <c r="D17">
-        <v>340</v>
-      </c>
-      <c r="E17">
-        <v>1000</v>
-      </c>
-      <c r="F17">
-        <v>170</v>
-      </c>
-      <c r="G17" t="s">
-        <v>58</v>
-      </c>
-      <c r="H17" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18">
-        <v>90</v>
-      </c>
-      <c r="D18">
-        <v>360</v>
-      </c>
-      <c r="E18">
-        <v>1000</v>
-      </c>
-      <c r="F18">
-        <v>180</v>
-      </c>
-      <c r="G18" t="s">
-        <v>60</v>
-      </c>
-      <c r="H18" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19">
-        <v>90</v>
-      </c>
-      <c r="D19">
-        <v>380</v>
-      </c>
-      <c r="E19">
-        <v>1000</v>
-      </c>
-      <c r="F19">
-        <v>190</v>
-      </c>
-      <c r="G19" t="s">
-        <v>62</v>
-      </c>
-      <c r="H19" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20">
-        <v>90</v>
-      </c>
-      <c r="D20">
-        <v>400</v>
-      </c>
-      <c r="E20">
-        <v>1000</v>
-      </c>
-      <c r="F20">
-        <v>200</v>
-      </c>
-      <c r="G20" t="s">
-        <v>64</v>
-      </c>
-      <c r="H20" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21">
-        <v>180</v>
-      </c>
-      <c r="D21">
-        <v>1000</v>
-      </c>
-      <c r="E21">
-        <v>1000</v>
-      </c>
-      <c r="F21">
-        <v>500</v>
-      </c>
-      <c r="G21" t="s">
-        <v>66</v>
-      </c>
-      <c r="H21" t="s">
-        <v>67</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>